--- a/artfynd/A 62767-2022 artfynd.xlsx
+++ b/artfynd/A 62767-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62767-2022 artfynd.xlsx
+++ b/artfynd/A 62767-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1838,133 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126415738</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57742</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hygge NV Årskogen, Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621832</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6892363</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62767-2022 artfynd.xlsx
+++ b/artfynd/A 62767-2022 artfynd.xlsx
@@ -1843,7 +1843,7 @@
         <v>126415738</v>
       </c>
       <c r="B12" t="n">
-        <v>57742</v>
+        <v>57743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62767-2022 artfynd.xlsx
+++ b/artfynd/A 62767-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104465835</v>
+        <v>126415738</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,35 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Årskogen, Hls</t>
+          <t>Hygge NV Årskogen, Årskogen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621835.7082929302</v>
+        <v>621832</v>
       </c>
       <c r="R2" t="n">
-        <v>6892368.059672508</v>
+        <v>6892363</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +760,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +790,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emelie Westin</t>
+          <t>Anders Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emelie Westin</t>
+          <t>Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104465831</v>
+        <v>104465783</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +832,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621818.6259312574</v>
+        <v>621976</v>
       </c>
       <c r="R3" t="n">
-        <v>6892464.78572142</v>
+        <v>6892422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +874,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104465796</v>
+        <v>104465784</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621977.9056844244</v>
+        <v>621825</v>
       </c>
       <c r="R4" t="n">
-        <v>6892777.990794856</v>
+        <v>6892556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +975,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104465795</v>
+        <v>104465789</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621962.1885110387</v>
+        <v>621860</v>
       </c>
       <c r="R5" t="n">
-        <v>6892836.851306496</v>
+        <v>6892596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1076,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104465832</v>
+        <v>104465795</v>
       </c>
       <c r="B6" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1135,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621786.873034421</v>
+        <v>621962</v>
       </c>
       <c r="R6" t="n">
-        <v>6892435.560779993</v>
+        <v>6892837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1177,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104465783</v>
+        <v>104465796</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1236,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621976.2478064521</v>
+        <v>621978</v>
       </c>
       <c r="R7" t="n">
-        <v>6892421.806284806</v>
+        <v>6892778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,19 +1278,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,12 +1310,7 @@
         <v>104465797</v>
       </c>
       <c r="B8" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621922.1282773325</v>
+        <v>621922</v>
       </c>
       <c r="R8" t="n">
-        <v>6892726.373158159</v>
+        <v>6892726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,19 +1379,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1492,15 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104465841</v>
+        <v>104465798</v>
       </c>
       <c r="B9" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1443,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1536,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621925.5500985514</v>
+        <v>621878</v>
       </c>
       <c r="R9" t="n">
-        <v>6892787.329870292</v>
+        <v>6892718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,19 +1485,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104465833</v>
+        <v>104465800</v>
       </c>
       <c r="B10" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1544,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621807.0127473369</v>
+        <v>621862</v>
       </c>
       <c r="R10" t="n">
-        <v>6892448.923099554</v>
+        <v>6892721</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,19 +1586,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,15 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104465834</v>
+        <v>104465801</v>
       </c>
       <c r="B11" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1645,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621819.0854734021</v>
+        <v>621856</v>
       </c>
       <c r="R11" t="n">
-        <v>6892439.062972855</v>
+        <v>6892714</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,19 +1687,9 @@
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126415738</v>
+        <v>104465802</v>
       </c>
       <c r="B12" t="n">
-        <v>57743</v>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,57 +1727,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102626</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hygge NV Årskogen, Årskogen, Hls</t>
+          <t>Årskogen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621832</v>
+        <v>621817</v>
       </c>
       <c r="R12" t="n">
-        <v>6892363</v>
+        <v>6892777</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,22 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:40</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,15 +1805,1535 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Johansson</t>
+          <t>Emelie Westin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Johansson</t>
+          <t>Emelie Westin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104465828</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6892524</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104465829</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>621779</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6892526</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104465831</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>621819</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6892465</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104465832</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>621787</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6892435</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104465833</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>621807</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6892449</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104465834</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>621819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6892439</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104465835</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>621836</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6892368</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104465836</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>621817</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6892371</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104465841</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>621926</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6892787</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>104465842</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>621933</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6892797</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104465843</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>621942</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6892800</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104465844</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>621948</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6892814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>i dike</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104465846</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>621943</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6892821</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104465850</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>621863</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6892810</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104465851</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Årskogen, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>621839</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6892814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gnarp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62767-2022 artfynd.xlsx
+++ b/artfynd/A 62767-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126415738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465789</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465795</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465796</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465797</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465798</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465800</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465801</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465802</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465828</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,6 +2081,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465829</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465831</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465832</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2319,6 +2399,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465833</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465834</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2521,6 +2611,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465835</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2622,6 +2717,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465836</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2723,6 +2823,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465841</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2824,6 +2929,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465842</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2925,6 +3035,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465843</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3031,6 +3146,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465844</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3132,6 +3252,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465846</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3233,6 +3358,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465850</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3334,8 +3464,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104465851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>